--- a/data/2026/cjsl/fall/soccer-legion-fc-u11-boys-blue-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-legion-fc-u11-boys-blue-2015-2016.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/soccer-legion-fc-u11-boys-blue-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-legion-fc-u11-boys-blue-2015-2016.xlsx
@@ -75,10 +75,10 @@
     <col min="3" max="3" bestFit="1" customWidth="1" width="13.200000000000001"/>
     <col min="4" max="4" bestFit="1" customWidth="1" width="45.1"/>
     <col min="5" max="5" bestFit="1" customWidth="1" width="7.700000000000001"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" width="44.0"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" width="52.800000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="50.6"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="19.8"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -154,7 +154,7 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Scorpio 2015/2016</t>
+          <t>Soccer Stars United Met Oval - SSU White 2015/2016 (Formerly Scorpio)</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>12:00 EDT</t>
+          <t>14:00 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Juventus Academy NY CJSL Vieri - B2016/2017</t>
+          <t>Soccer Legion FC U11 Boys Blue (2015/2016)</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 2</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Soccer Legion FC U11 Boys Blue (2015/2016)</t>
+          <t>Eleftheria Pancyprian Soccer Club EPSC 2015/2016 White</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 60</t>
+          <t>Brooklyn Bridge Park Pier 5  - Field 3 </t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,27 +214,27 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Saturday, October 17, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>14:00 EDT</t>
+          <t>12:00 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Soccer Legion FC U11 Boys Blue (2015/2016)</t>
+          <t>B&amp;G Soccer Academy &amp; B2015/16 GLADIATORS</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -244,12 +244,12 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Eleftheria Pancyprian Soccer Club EPSC 2015/2016 White</t>
+          <t>Soccer Legion FC U11 Boys Blue (2015/2016)</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn Bridge Park Pier 5  - Field 3 </t>
+          <t>Van Cortlandt Park - C</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,21 +265,21 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 17, 2026</t>
+          <t>Sunday, October 18, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>12:00 EDT</t>
+          <t>08:15 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>B&amp;G Soccer Academy &amp; B2015/16 GLADIATORS</t>
+          <t>Juventus Academy NY CJSL Vieri - B2016/2017</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -294,7 +294,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Van Cortlandt Park - C</t>
+          <t>Randall's Island - 6</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/soccer-legion-fc-u11-boys-blue-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-legion-fc-u11-boys-blue-2015-2016.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 3</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
